--- a/keyboards/kiwikey/buildbox/keycodes_converter.xlsx
+++ b/keyboards/kiwikey/buildbox/keycodes_converter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\qmk_firmware\keyboards\kiwikey\buildbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4076D1-76F0-4122-852F-EF72A1EA51BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790DD1F6-B3F3-4ECC-BB7B-3C56C06C6F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1965" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4649" uniqueCount="1625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4650" uniqueCount="1625">
   <si>
     <t>KC_NO</t>
   </si>
@@ -31234,6 +31234,9 @@
       <c r="B707" s="2" t="s">
         <v>1411</v>
       </c>
+      <c r="C707" s="3" t="s">
+        <v>1481</v>
+      </c>
       <c r="D707" s="4" t="s">
         <v>1486</v>
       </c>
@@ -31253,14 +31256,14 @@
       </c>
       <c r="I707" s="3" t="str">
         <f t="shared" ref="I707:I737" si="48">IF(C707="","",C707)</f>
-        <v/>
+        <v>=</v>
       </c>
       <c r="J707" s="5" t="s">
         <v>1484</v>
       </c>
       <c r="K707" s="2" t="str">
         <f t="shared" ref="K707:K737" si="49">IF(I707="","",_xlfn.CONCAT(D707:J707))</f>
-        <v/>
+        <v xml:space="preserve">    X (  QK_USER_1                                    , 0x7E41,    "="     ) \</v>
       </c>
     </row>
     <row r="708" spans="1:11" x14ac:dyDescent="0.25">
@@ -32376,6 +32379,7 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="256" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -36627,7 +36631,7 @@
     <row r="707" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" s="1" t="str">
         <f>IF(List!K707="","",List!K707)</f>
-        <v/>
+        <v xml:space="preserve">    X (  QK_USER_1                                    , 0x7E41,    "="     ) \</v>
       </c>
     </row>
     <row r="708" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
